--- a/modules/brand/templates/Survey_Structure_Brand_Config_Template.xlsx
+++ b/modules/brand/templates/Survey_Structure_Brand_Config_Template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="609">
   <si>
     <t xml:space="preserve">TURAS Survey Structure — Project Settings</t>
   </si>
@@ -525,10 +525,10 @@
     <t xml:space="preserve">[Optional] TABS ONLY — exclude from mean/index calculations (e.g. Don't know, N/A). Y = exclude.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — numeric weight for index calculation. Rating: scale value (1-5). Likert: custom weight (-100 to 100).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — alternative numeric value for calculations (overrides OptionText if present).</t>
+    <t xml:space="preserve">[Optional] TABS ONLY — numeric weight for the Likert index (e.g. -100 to 100). Every option needs one; with none, no index row is written. Rating means don't use it - see OptionValue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY — numeric value used for calculations instead of OptionText. Scores Rating means and box/NET ordering; leave blank when OptionText is already the number.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] TABS ONLY — group options into summary rows (e.g. 'Top 2 Box', 'Satisfied', 'Promoters'). Options sharing a BoxCategory label are summed.</t>
@@ -717,6 +717,9 @@
     <t xml:space="preserve">Colour</t>
   </si>
   <si>
+    <t xml:space="preserve">BrandCodeAlias</t>
+  </si>
+  <si>
     <t xml:space="preserve">[REQUIRED] Full category display name (e.g. 'Dry Seasonings &amp; Spices'). Must match the Category column in Brand_Config Categories sheet.</t>
   </si>
   <si>
@@ -738,6 +741,9 @@
     <t xml:space="preserve">[Optional] Optional hex colour (#RRGGBB) for this brand in charts and chips. Focal brand should match colour_focal in Brand_Config. Leave blank to use category defaults.</t>
   </si>
   <si>
+    <t xml:space="preserve">[Optional] Optional alternate suffix / option-value the data uses for this brand in this category. Leave blank when BrandCode matches the data. Set when the Alchemer survey was programmed with a different SKU than the canonical BrandCode (e.g. 'FNF' for a brand whose canonical code is 'FNFPS'). The engine accepts BOTH BrandCode and BrandCodeAlias when resolving per-brand columns and slot values.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dry Seasonings &amp; Spices</t>
   </si>
   <si>
@@ -1164,6 +1170,15 @@
     <t xml:space="preserve">AssetLabel</t>
   </si>
   <si>
+    <t xml:space="preserve">SeenQuestionCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BrandQuestionCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MediaQuestionCode</t>
+  </si>
+  <si>
     <t xml:space="preserve">MediaType</t>
   </si>
   <si>
@@ -1179,7 +1194,16 @@
     <t xml:space="preserve">[REQUIRED] Category this asset is associated with, or 'ALL' for brand-level assets.</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] BrandCode of the brand this asset belongs to.</t>
+    <t xml:space="preserve">[REQUIRED] BrandCode of the brand this asset belongs to (the code from the Brands sheet, not the label).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Data column for the recognition question for this asset (1 = recognised). Referenced by the QuestionMap reach.seen.{asset} row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Data column for the brand attribution question. Cell values are a BrandCode from this category's Brands list, DK or OTHER (closed list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Data column root for the 'Where did you see it?' multi-mention question. Values are MediaCode entries from the ReachMedia sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] Media channel type for grouping in the panel (e.g. TV, OOH, Digital, Print, Radio).</t>
@@ -1191,7 +1215,16 @@
     <t xml:space="preserve">TV_AD_Q1_2026</t>
   </si>
   <si>
-    <t xml:space="preserve">TV ad — Q1 2026</t>
+    <t xml:space="preserve">TV ad, Q1 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REACH_SEEN_TV_AD_Q1_2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REACH_BRAND_TV_AD_Q1_2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REACH_MEDIA_TV_AD_Q1_2026</t>
   </si>
   <si>
     <t xml:space="preserve">TV</t>
@@ -1203,19 +1236,37 @@
     <t xml:space="preserve">OOH_NATIONAL_JAN</t>
   </si>
   <si>
-    <t xml:space="preserve">Billboard — January 2026</t>
+    <t xml:space="preserve">Billboard, January 2026</t>
   </si>
   <si>
     <t xml:space="preserve">ALL</t>
   </si>
   <si>
+    <t xml:space="preserve">REACH_SEEN_OOH_NATIONAL_JAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REACH_BRAND_OOH_NATIONAL_JAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REACH_MEDIA_OOH_NATIONAL_JAN</t>
+  </si>
+  <si>
     <t xml:space="preserve">OOH</t>
   </si>
   <si>
     <t xml:space="preserve">DIGITAL_FACEBOOK_FEB</t>
   </si>
   <si>
-    <t xml:space="preserve">Facebook ad — February 2026</t>
+    <t xml:space="preserve">Facebook ad, February 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REACH_SEEN_DIGITAL_FACEBOOK_FEB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REACH_BRAND_DIGITAL_FACEBOOK_FEB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REACH_MEDIA_DIGITAL_FACEBOOK_FEB</t>
   </si>
   <si>
     <t xml:space="preserve">Digital</t>
@@ -2677,12 +2728,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3">
@@ -2693,10 +2744,10 @@
         <v>224</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>151</v>
@@ -2704,33 +2755,33 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>1</v>
@@ -2738,16 +2789,16 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>2</v>
@@ -2755,16 +2806,16 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>3</v>
@@ -2772,16 +2823,16 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>4</v>
@@ -2789,16 +2840,16 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>5</v>
@@ -3044,12 +3095,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3">
@@ -3060,10 +3111,10 @@
         <v>224</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>151</v>
@@ -3071,33 +3122,33 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>1</v>
@@ -3105,16 +3156,16 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>2</v>
@@ -3122,16 +3173,16 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>3</v>
@@ -3139,16 +3190,16 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>4</v>
@@ -3319,26 +3370,29 @@
     <col min="2" max="2" width="35.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="24.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="40.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="24.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="18.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="40.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>64</v>
@@ -3347,89 +3401,134 @@
         <v>220</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>379</v>
+        <v>381</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>385</v>
+        <v>390</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>389</v>
+        <v>397</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="F6" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="I6" s="17" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="F7" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3440,6 +3539,9 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
@@ -3448,6 +3550,9 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -3456,6 +3561,9 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -3464,6 +3572,9 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -3472,6 +3583,9 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -3480,6 +3594,9 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -3488,6 +3605,9 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -3496,6 +3616,9 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -3504,6 +3627,9 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -3512,6 +3638,9 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -3520,6 +3649,9 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -3528,6 +3660,9 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -3536,6 +3671,9 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
@@ -3544,6 +3682,9 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
@@ -3552,6 +3693,9 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
     </row>
     <row r="23">
       <c r="A23" s="11"/>
@@ -3560,6 +3704,9 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
     </row>
     <row r="24">
       <c r="A24" s="11"/>
@@ -3568,6 +3715,9 @@
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
     </row>
     <row r="25">
       <c r="A25" s="11"/>
@@ -3576,6 +3726,9 @@
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
@@ -3584,6 +3737,9 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
     </row>
     <row r="27">
       <c r="A27" s="11"/>
@@ -3592,11 +3748,14 @@
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3607,7 +3766,7 @@
           <x14:formula1>
             <xm:f>"TV,Digital,OOH,Print,Radio,Sponsorship,Other"</xm:f>
           </x14:formula1>
-          <xm:sqref>E5:E27</xm:sqref>
+          <xm:sqref>H5:H27</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3627,20 +3786,20 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>151</v>
@@ -3648,21 +3807,21 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>1</v>
@@ -3670,10 +3829,10 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>2</v>
@@ -3681,10 +3840,10 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="C7" s="17" t="n">
         <v>3</v>
@@ -3692,10 +3851,10 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="C8" s="17" t="n">
         <v>4</v>
@@ -3703,10 +3862,10 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>5</v>
@@ -3714,10 +3873,10 @@
     </row>
     <row r="10">
       <c r="A10" s="17" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="C10" s="17" t="n">
         <v>6</v>
@@ -3725,10 +3884,10 @@
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="C11" s="17" t="n">
         <v>7</v>
@@ -3817,12 +3976,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3">
@@ -3830,74 +3989,74 @@
         <v>64</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>107</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>170</v>
@@ -3905,25 +4064,25 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>107</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>170</v>
@@ -3931,54 +4090,54 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -4217,97 +4376,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -4430,12 +4589,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
     </row>
     <row r="4">
@@ -4449,10 +4608,10 @@
         <v>63</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" ht="55" customHeight="1">
@@ -4460,16 +4619,16 @@
         <v>135</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>177</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6" ht="55" customHeight="1">
@@ -4477,16 +4636,16 @@
         <v>84</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>177</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" ht="55" customHeight="1">
@@ -4494,33 +4653,33 @@
         <v>89</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>177</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" ht="55" customHeight="1">
@@ -4528,16 +4687,16 @@
         <v>139</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>177</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" ht="55" customHeight="1">
@@ -4545,67 +4704,67 @@
         <v>144</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>177</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>177</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>508</v>
+        <v>525</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>177</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -4631,23 +4790,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>70</v>
@@ -4655,240 +4814,240 @@
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>95</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="14" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>524</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>528</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>130</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>107</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="14" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>111</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>114</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="14" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="14" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="14" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="14" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>122</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="14" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>126</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1">
@@ -4899,10 +5058,10 @@
         <v>87</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1">
@@ -4913,66 +5072,66 @@
         <v>92</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>
@@ -10803,6 +10962,7 @@
     <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="12.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="16.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="18.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10837,36 +10997,42 @@
       <c r="G3" s="8" t="s">
         <v>228</v>
       </c>
+      <c r="H3" s="8" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>170</v>
@@ -10881,15 +11047,18 @@
         <v>172</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>238</v>
+        <v>240</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>173</v>
@@ -10906,19 +11075,22 @@
       <c r="G6" s="17" t="s">
         <v>14</v>
       </c>
+      <c r="H6" s="17" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>3</v>
@@ -10929,13 +11101,16 @@
       <c r="G7" s="17" t="s">
         <v>14</v>
       </c>
+      <c r="H7" s="17" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>175</v>
@@ -10952,13 +11127,16 @@
       <c r="G8" s="17" t="s">
         <v>14</v>
       </c>
+      <c r="H8" s="17" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>170</v>
@@ -10973,21 +11151,24 @@
         <v>172</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>238</v>
+        <v>240</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>2</v>
@@ -10996,6 +11177,9 @@
         <v>47</v>
       </c>
       <c r="G10" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>14</v>
       </c>
     </row>
@@ -11007,6 +11191,7 @@
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -11016,6 +11201,7 @@
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -11025,6 +11211,7 @@
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -11034,6 +11221,7 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -11043,6 +11231,7 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -11052,6 +11241,7 @@
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -11061,6 +11251,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -11070,6 +11261,7 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -11079,6 +11271,7 @@
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -11088,6 +11281,7 @@
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
@@ -11097,6 +11291,7 @@
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
@@ -11106,6 +11301,7 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
     </row>
     <row r="23">
       <c r="A23" s="11"/>
@@ -11115,6 +11311,7 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
     </row>
     <row r="24">
       <c r="A24" s="11"/>
@@ -11124,6 +11321,7 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
     </row>
     <row r="25">
       <c r="A25" s="11"/>
@@ -11133,6 +11331,7 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
@@ -11142,6 +11341,7 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
     </row>
     <row r="27">
       <c r="A27" s="11"/>
@@ -11151,6 +11351,7 @@
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
     </row>
     <row r="28">
       <c r="A28" s="11"/>
@@ -11160,6 +11361,7 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
     </row>
     <row r="29">
       <c r="A29" s="11"/>
@@ -11169,6 +11371,7 @@
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
     </row>
     <row r="30">
       <c r="A30" s="11"/>
@@ -11178,6 +11381,7 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
     </row>
     <row r="31">
       <c r="A31" s="11"/>
@@ -11187,6 +11391,7 @@
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
       <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
     </row>
     <row r="32">
       <c r="A32" s="11"/>
@@ -11196,6 +11401,7 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
     </row>
     <row r="33">
       <c r="A33" s="11"/>
@@ -11205,6 +11411,7 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
     </row>
     <row r="34">
       <c r="A34" s="11"/>
@@ -11214,6 +11421,7 @@
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
     </row>
     <row r="35">
       <c r="A35" s="11"/>
@@ -11223,6 +11431,7 @@
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
     </row>
     <row r="36">
       <c r="A36" s="11"/>
@@ -11232,6 +11441,7 @@
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
     </row>
     <row r="37">
       <c r="A37" s="11"/>
@@ -11241,6 +11451,7 @@
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
     </row>
     <row r="38">
       <c r="A38" s="11"/>
@@ -11250,6 +11461,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
     </row>
     <row r="39">
       <c r="A39" s="11"/>
@@ -11259,6 +11471,7 @@
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
     </row>
     <row r="40">
       <c r="A40" s="11"/>
@@ -11268,6 +11481,7 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
     </row>
     <row r="41">
       <c r="A41" s="11"/>
@@ -11277,6 +11491,7 @@
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
     </row>
     <row r="42">
       <c r="A42" s="11"/>
@@ -11286,6 +11501,7 @@
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
     </row>
     <row r="43">
       <c r="A43" s="11"/>
@@ -11295,6 +11511,7 @@
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
       <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
     </row>
     <row r="44">
       <c r="A44" s="11"/>
@@ -11304,6 +11521,7 @@
       <c r="E44" s="11"/>
       <c r="F44" s="11"/>
       <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
     </row>
     <row r="45">
       <c r="A45" s="11"/>
@@ -11313,6 +11531,7 @@
       <c r="E45" s="11"/>
       <c r="F45" s="11"/>
       <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
     </row>
     <row r="46">
       <c r="A46" s="11"/>
@@ -11322,6 +11541,7 @@
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
     </row>
     <row r="47">
       <c r="A47" s="11"/>
@@ -11331,6 +11551,7 @@
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
       <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
     </row>
     <row r="48">
       <c r="A48" s="11"/>
@@ -11340,6 +11561,7 @@
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
       <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
     </row>
     <row r="49">
       <c r="A49" s="11"/>
@@ -11349,6 +11571,7 @@
       <c r="E49" s="11"/>
       <c r="F49" s="11"/>
       <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
     </row>
     <row r="50">
       <c r="A50" s="11"/>
@@ -11358,6 +11581,7 @@
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
     </row>
     <row r="51">
       <c r="A51" s="11"/>
@@ -11367,6 +11591,7 @@
       <c r="E51" s="11"/>
       <c r="F51" s="11"/>
       <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
     </row>
     <row r="52">
       <c r="A52" s="11"/>
@@ -11376,6 +11601,7 @@
       <c r="E52" s="11"/>
       <c r="F52" s="11"/>
       <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
     </row>
     <row r="53">
       <c r="A53" s="11"/>
@@ -11385,6 +11611,7 @@
       <c r="E53" s="11"/>
       <c r="F53" s="11"/>
       <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
     </row>
     <row r="54">
       <c r="A54" s="11"/>
@@ -11394,6 +11621,7 @@
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
     </row>
     <row r="55">
       <c r="A55" s="11"/>
@@ -11403,6 +11631,7 @@
       <c r="E55" s="11"/>
       <c r="F55" s="11"/>
       <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
     </row>
     <row r="56">
       <c r="A56" s="11"/>
@@ -11412,6 +11641,7 @@
       <c r="E56" s="11"/>
       <c r="F56" s="11"/>
       <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
     </row>
     <row r="57">
       <c r="A57" s="11"/>
@@ -11421,6 +11651,7 @@
       <c r="E57" s="11"/>
       <c r="F57" s="11"/>
       <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
     </row>
     <row r="58">
       <c r="A58" s="11"/>
@@ -11430,6 +11661,7 @@
       <c r="E58" s="11"/>
       <c r="F58" s="11"/>
       <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
     </row>
     <row r="59">
       <c r="A59" s="11"/>
@@ -11439,6 +11671,7 @@
       <c r="E59" s="11"/>
       <c r="F59" s="11"/>
       <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
     </row>
     <row r="60">
       <c r="A60" s="11"/>
@@ -11448,11 +11681,12 @@
       <c r="E60" s="11"/>
       <c r="F60" s="11"/>
       <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="E5:E60">
@@ -11491,12 +11725,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3">
@@ -11507,10 +11741,10 @@
         <v>224</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>151</v>
@@ -11518,33 +11752,33 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>1</v>
@@ -11552,16 +11786,16 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>2</v>
@@ -11569,16 +11803,16 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>3</v>
@@ -11586,16 +11820,16 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>4</v>
@@ -11603,16 +11837,16 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>5</v>
@@ -12068,12 +12302,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3">
@@ -12084,10 +12318,10 @@
         <v>224</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>151</v>
@@ -12095,33 +12329,33 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>1</v>
@@ -12129,16 +12363,16 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>2</v>
@@ -12146,16 +12380,16 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>3</v>
@@ -12163,16 +12397,16 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>4</v>
@@ -12418,26 +12652,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>70</v>
@@ -12445,24 +12679,24 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>122</v>
@@ -12471,35 +12705,35 @@
         <v>84</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>84</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>84</v>
@@ -12508,15 +12742,15 @@
         <v>14</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>135</v>
@@ -12525,7 +12759,7 @@
         <v>14</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
@@ -12774,60 +13008,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>1</v>
@@ -12835,16 +13069,16 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>2</v>
@@ -12852,16 +13086,16 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>3</v>
@@ -12869,16 +13103,16 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>4</v>
@@ -12886,16 +13120,16 @@
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>5</v>
@@ -12903,13 +13137,13 @@
     </row>
     <row r="10">
       <c r="A10" s="17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>177</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>178</v>
@@ -12920,13 +13154,13 @@
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>179</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>180</v>
@@ -12937,16 +13171,16 @@
     </row>
     <row r="12">
       <c r="A12" s="17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>181</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>3</v>
@@ -12954,13 +13188,13 @@
     </row>
     <row r="13">
       <c r="A13" s="17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>183</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>184</v>
@@ -12971,13 +13205,13 @@
     </row>
     <row r="14">
       <c r="A14" s="17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>185</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>186</v>
@@ -12988,16 +13222,16 @@
     </row>
     <row r="15">
       <c r="A15" s="17" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>177</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E15" s="17" t="n">
         <v>1</v>
@@ -13005,16 +13239,16 @@
     </row>
     <row r="16">
       <c r="A16" s="17" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>179</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>2</v>

--- a/modules/brand/templates/Survey_Structure_Brand_Config_Template.xlsx
+++ b/modules/brand/templates/Survey_Structure_Brand_Config_Template.xlsx
@@ -30,7 +30,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="609">
   <si>
-    <t xml:space="preserve">TURAS Survey Structure — Project Settings</t>
+    <t xml:space="preserve">TURAS Survey Structure: Project Settings</t>
   </si>
   <si>
     <t xml:space="preserve">Shared across brand, tabs, and tracker modules. Values here must match Brand_Config.xlsx.</t>
@@ -207,7 +207,7 @@
     <t xml:space="preserve">Question Definitions  [SHARED: used by brand module AND tabs module]</t>
   </si>
   <si>
-    <t xml:space="preserve">One row per question. Brand module: follow the naming convention in the Question Naming Guide sheet — roles are inferred automatically from question code prefixes (BRANDAWARE_, BRANDATTR_, etc.). Tabs module: use any QuestionCode and set Variable_Type. Blue rows are examples.</t>
+    <t xml:space="preserve">One row per question. Brand module: follow the naming convention in the Question Naming Guide sheet: roles are inferred automatically from question code prefixes (BRANDAWARE_, BRANDATTR_, etc.). Tabs module: use any QuestionCode and set Variable_Type. Blue rows are examples.</t>
   </si>
   <si>
     <t xml:space="preserve">QuestionCode</t>
@@ -243,10 +243,10 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] Unique code matching the column name prefix in the data file (case-sensitive). For slot-indexed questions (Multi_Mention brand batteries) use the ROOT code — the role inferrer adds the _1, _2 ... slot suffix automatically. Examples: BRANDAWARE_DSS, DEMO_AGE, Q_Gender.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[REQUIRED] Full question wording as shown in output reports. For brand batteries use a short descriptive label (e.g. 'Brand awareness — Dry Seasonings &amp; Spices').</t>
+    <t xml:space="preserve">[REQUIRED] Unique code matching the column name prefix in the data file (case-sensitive). For slot-indexed questions (Multi_Mention brand batteries) use the ROOT code. The role inferrer adds the _1, _2 ... slot suffix automatically. Examples: BRANDAWARE_DSS, DEMO_AGE, Q_Gender.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Full question wording as shown in output reports. For brand batteries use a short descriptive label (e.g. 'Brand awareness: Dry Seasonings &amp; Spices').</t>
   </si>
   <si>
     <t xml:space="preserve">[REQUIRED] Question type. Brand module uses Single_Response/Multi_Mention. Tabs module uses the full type set. See Variable Type Reference sheet for full descriptions.</t>
@@ -255,22 +255,22 @@
     <t xml:space="preserve">[REQUIRED] Number of data columns: 1 for most types; for Multi_Mention slot-indexed questions enter the number of slots (brands + 1 for NONE). For tabs Ranking enter the number of items ranked.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] TABS: section/grouping label for output organisation (e.g. 'Demographics', 'Satisfaction'). BRAND: informational only — the brand module infers battery and category from the question code naming convention.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — required for Ranking questions. 'Position' = each item column holds rank position number. 'Item' = each rank column holds item code.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — for Ranking: how many items each respondent ranks (e.g. 3 for 'rank your top 3').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — for Ranking: does Rank 1 mean best or worst?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — for Numeric questions: minimum expected value (used for validation and binning).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — for Numeric questions: maximum expected value.</t>
+    <t xml:space="preserve">[Optional] TABS: section/grouping label for output organisation (e.g. 'Demographics', 'Satisfaction'). BRAND: informational only, the brand module infers battery and category from the question code naming convention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY: required for Ranking questions. 'Position' = each item column holds rank position number. 'Item' = each rank column holds item code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY, for Ranking: how many items each respondent ranks (e.g. 3 for 'rank your top 3').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY, for Ranking: does Rank 1 mean best or worst?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY, for Numeric questions: minimum expected value (used for validation and binning).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY, for Numeric questions: maximum expected value.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] Internal notes (not shown in output).</t>
@@ -318,7 +318,7 @@
     <t xml:space="preserve">BRANDAWARE_DSS</t>
   </si>
   <si>
-    <t xml:space="preserve">Brands heard of — Dry Seasonings &amp; Spices</t>
+    <t xml:space="preserve">Brands heard of: Dry Seasonings &amp; Spices</t>
   </si>
   <si>
     <t xml:space="preserve">Awareness</t>
@@ -330,7 +330,7 @@
     <t xml:space="preserve">BRANDATTR_DSS_CEP01</t>
   </si>
   <si>
-    <t xml:space="preserve">CEP 1 — Good for a quick weeknight meal (DSS)</t>
+    <t xml:space="preserve">CEP 1: Good for a quick weeknight meal (DSS)</t>
   </si>
   <si>
     <t xml:space="preserve">Mental Availability</t>
@@ -342,7 +342,7 @@
     <t xml:space="preserve">BRANDATT1_DSS_IPK</t>
   </si>
   <si>
-    <t xml:space="preserve">Brand attitude — IPK (Dry Seasonings)</t>
+    <t xml:space="preserve">Brand attitude: IPK (Dry Seasonings)</t>
   </si>
   <si>
     <t xml:space="preserve">Funnel</t>
@@ -354,7 +354,7 @@
     <t xml:space="preserve">BRANDPEN2_DSS</t>
   </si>
   <si>
-    <t xml:space="preserve">Brands bought in last 3 months — Dry Seasonings</t>
+    <t xml:space="preserve">Brands bought in last 3 months: Dry Seasonings</t>
   </si>
   <si>
     <t xml:space="preserve">Penetration</t>
@@ -366,7 +366,7 @@
     <t xml:space="preserve">BRANDPEN3_DSS</t>
   </si>
   <si>
-    <t xml:space="preserve">Purchase frequency (bought X times) — Dry Seasonings</t>
+    <t xml:space="preserve">Purchase frequency (bought X times): Dry Seasonings</t>
   </si>
   <si>
     <t xml:space="preserve">Convention: BRANDPEN3_{CAT}. Per-brand frequency sum. Role: repertoire.freq.DSS</t>
@@ -375,7 +375,7 @@
     <t xml:space="preserve">WOM_POS_REC_DSS</t>
   </si>
   <si>
-    <t xml:space="preserve">Received positive WOM — Dry Seasonings</t>
+    <t xml:space="preserve">Received positive WOM: Dry Seasonings</t>
   </si>
   <si>
     <t xml:space="preserve">WOM</t>
@@ -423,7 +423,7 @@
     <t xml:space="preserve">BRANDPEN1_DSS</t>
   </si>
   <si>
-    <t xml:space="preserve">Brands bought in last 12 months — Dry Seasonings</t>
+    <t xml:space="preserve">Brands bought in last 12 months: Dry Seasonings</t>
   </si>
   <si>
     <t xml:space="preserve">Convention: BRANDPEN1_{CAT}. Role: funnel.bought_longer.DSS</t>
@@ -438,7 +438,7 @@
     <t xml:space="preserve">Single_Mention</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard tabs question — use in Crosstab_Config as banner</t>
+    <t xml:space="preserve">Standard tabs question: use in Crosstab_Config as banner</t>
   </si>
   <si>
     <t xml:space="preserve">Q_Satisfaction</t>
@@ -453,7 +453,7 @@
     <t xml:space="preserve">Satisfaction</t>
   </si>
   <si>
-    <t xml:space="preserve">Tabs Rating question — generates mean score in crosstabs</t>
+    <t xml:space="preserve">Tabs Rating question: generates mean score in crosstabs</t>
   </si>
   <si>
     <t xml:space="preserve">Q_NPS</t>
@@ -468,7 +468,7 @@
     <t xml:space="preserve">Loyalty</t>
   </si>
   <si>
-    <t xml:space="preserve">Tabs NPS — auto-calculates Promoters/Passives/Detractors</t>
+    <t xml:space="preserve">Tabs NPS: auto-calculates Promoters/Passives/Detractors</t>
   </si>
   <si>
     <t xml:space="preserve">Response Option Definitions  [SHARED: used by brand module AND tabs module]</t>
@@ -522,22 +522,22 @@
     <t xml:space="preserve">[REQUIRED] Y = show this option in output tables. N = hide (useful for suppressing 'None of the above' rows in some views but not others).</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — exclude from mean/index calculations (e.g. Don't know, N/A). Y = exclude.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — numeric weight for the Likert index (e.g. -100 to 100). Every option needs one; with none, no index row is written. Rating means don't use it - see OptionValue.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — numeric value used for calculations instead of OptionText. Scores Rating means and box/NET ordering; leave blank when OptionText is already the number.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — group options into summary rows (e.g. 'Top 2 Box', 'Satisfied', 'Promoters'). Options sharing a BoxCategory label are summed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — for Numeric binning: minimum value of this bin (e.g. 18 for '18-24' age band).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY — for Numeric binning: maximum value of this bin (e.g. 24 for '18-24' age band).</t>
+    <t xml:space="preserve">[Optional] TABS ONLY: exclude from mean/index calculations (e.g. Don't know, N/A). Y = exclude.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY: numeric weight for the Likert index (e.g. -100 to 100). Every option needs one; with none, no index row is written. Rating means don't use it - see OptionValue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY: numeric value used for calculations instead of OptionText. Scores Rating means and box/NET ordering; leave blank when OptionText is already the number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY: group options into summary rows (e.g. 'Top 2 Box', 'Satisfied', 'Promoters'). Options sharing a BoxCategory label are summed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY, for Numeric binning: minimum value of this bin (e.g. 18 for '18-24' age band).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY, for Numeric binning: maximum value of this bin (e.g. 24 for '18-24' age band).</t>
   </si>
   <si>
     <t xml:space="preserve">IPK</t>
@@ -612,7 +612,7 @@
     <t xml:space="preserve">Top 2 Box</t>
   </si>
   <si>
-    <t xml:space="preserve">Composite Metric Definitions  [TABS MODULE ONLY — brand module ignores this sheet]</t>
+    <t xml:space="preserve">Composite Metric Definitions  [TABS MODULE ONLY: brand module ignores this sheet]</t>
   </si>
   <si>
     <t xml:space="preserve">Define composite scores that combine multiple questions. Blue rows are examples.</t>
@@ -639,7 +639,7 @@
     <t xml:space="preserve">ExcludeFromSummary</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] TABS ONLY — unique identifier for this composite score (e.g. COMP_SAT_OVERALL). Used as sheet name in output. Brand module ignores this sheet.</t>
+    <t xml:space="preserve">[REQUIRED] TABS ONLY: unique identifier for this composite score (e.g. COMP_SAT_OVERALL). Used as sheet name in output. Brand module ignores this sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">[REQUIRED] Display name shown in output (e.g. 'Overall Satisfaction Index').</t>
@@ -879,10 +879,10 @@
     <t xml:space="preserve">Has a wide product range</t>
   </si>
   <si>
-    <t xml:space="preserve">Question Role Map  [BRAND MODULE — optional overrides]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced: override or supplement the convention-inferred role map. Most questions do NOT need a row here — roles are inferred from naming conventions automatically. Use QuestionMap for: (1) cat_buying.frequency — needs OptionMapScale; (2) demographics questions that do not follow DEMO_ prefix; (3) ad hoc questions with adhoc. role prefix. Blue rows are examples.</t>
+    <t xml:space="preserve">Question Role Map  [BRAND MODULE: optional overrides]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced: override or supplement the convention-inferred role map. Most questions do NOT need a row here. Roles are inferred from naming conventions automatically. Use QuestionMap for: (1) cat_buying.frequency, which needs OptionMapScale; (2) demographics questions that do not follow DEMO_ prefix; (3) ad hoc questions with adhoc. role prefix. Blue rows are examples.</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -915,7 +915,7 @@
     <t xml:space="preserve">cat_buy_scale</t>
   </si>
   <si>
-    <t xml:space="preserve">Category buying frequency — coded response mapped to buy-rate multiplier via cat_buy_scale OptionMap</t>
+    <t xml:space="preserve">Category buying frequency: coded response mapped to buy-rate multiplier via cat_buy_scale OptionMap</t>
   </si>
   <si>
     <t xml:space="preserve">cat_buying.frequency.RM</t>
@@ -933,7 +933,7 @@
     <t xml:space="preserve">DEMO_PROVINCE</t>
   </si>
   <si>
-    <t xml:space="preserve">Province demographics — options defined in Options sheet by QuestionCode = DEMO_PROVINCE</t>
+    <t xml:space="preserve">Province demographics: options defined in Options sheet by QuestionCode = DEMO_PROVINCE</t>
   </si>
   <si>
     <t xml:space="preserve">adhoc.Q_BrandPerception.ALL</t>
@@ -945,7 +945,7 @@
     <t xml:space="preserve">Ad hoc question shown for ALL respondents (sample-wide scope). Scope = ALL means it appears in every category panel.</t>
   </si>
   <si>
-    <t xml:space="preserve">Option Scale Definitions  [BRAND MODULE — needed with QuestionMap OptionMapScale]</t>
+    <t xml:space="preserve">Option Scale Definitions  [BRAND MODULE: needed with QuestionMap OptionMapScale]</t>
   </si>
   <si>
     <t xml:space="preserve">Define reusable response scales referenced by OptionMapScale in QuestionMap. Each scale (cat_buy_scale, attitude_scale, etc.) appears as a block of rows. ClientCode must exactly match values in the data. Blue rows show the standard scales.</t>
@@ -1056,7 +1056,7 @@
     <t xml:space="preserve">I don't recognise this</t>
   </si>
   <si>
-    <t xml:space="preserve">Purchase Channel Definitions  [BRAND MODULE — Shopper Behaviour panel]</t>
+    <t xml:space="preserve">Purchase Channel Definitions  [BRAND MODULE: Shopper Behaviour panel]</t>
   </si>
   <si>
     <t xml:space="preserve">Purchase channel options for the Shopper Behaviour panel. One row per channel per category. ChannelCode must match values in CHANNEL_{CAT} data column. Blue rows are examples.</t>
@@ -1110,7 +1110,7 @@
     <t xml:space="preserve">Other</t>
   </si>
   <si>
-    <t xml:space="preserve">Pack Size Definitions  [BRAND MODULE — Shopper Behaviour panel]</t>
+    <t xml:space="preserve">Pack Size Definitions  [BRAND MODULE: Shopper Behaviour panel]</t>
   </si>
   <si>
     <t xml:space="preserve">Pack size options for the Shopper Behaviour panel. One row per pack size per category. PackCode must match values in PACK_{CAT} data column. Blue rows are examples.</t>
@@ -1158,7 +1158,7 @@
     <t xml:space="preserve">Different sizes at different times</t>
   </si>
   <si>
-    <t xml:space="preserve">Marketing Asset Definitions  [BRAND MODULE — Branded Reach panel, only if element_branded_reach = Y]</t>
+    <t xml:space="preserve">Marketing Asset Definitions  [BRAND MODULE: Branded Reach panel, only if element_branded_reach = Y]</t>
   </si>
   <si>
     <t xml:space="preserve">One row per marketing asset (ad, OOH execution, etc.) to test for recognition. AssetCode referenced by the Branded Reach engine. Leave blank if element_branded_reach = N. Blue rows are examples.</t>
@@ -1188,7 +1188,7 @@
     <t xml:space="preserve">[REQUIRED] Unique code for this marketing asset (e.g. TV_AD_Q1_2026, OOH_CAPE_JAN). Referenced by the Branded Reach engine.</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] Display label for the asset in outputs (e.g. 'TV ad — January 2026').</t>
+    <t xml:space="preserve">[REQUIRED] Display label for the asset in outputs (e.g. 'TV ad, January 2026').</t>
   </si>
   <si>
     <t xml:space="preserve">[REQUIRED] Category this asset is associated with, or 'ALL' for brand-level assets.</t>
@@ -1272,7 +1272,7 @@
     <t xml:space="preserve">Digital</t>
   </si>
   <si>
-    <t xml:space="preserve">Reach Media Channel Definitions  [BRAND MODULE — Branded Reach panel]</t>
+    <t xml:space="preserve">Reach Media Channel Definitions  [BRAND MODULE: Branded Reach panel]</t>
   </si>
   <si>
     <t xml:space="preserve">Media channels for the Branded Reach 'Where did you see this?' question. MediaCode must match values in the reach media attribution question in the data. Blue rows are examples.</t>
@@ -1326,7 +1326,7 @@
     <t xml:space="preserve">Other / unsure</t>
   </si>
   <si>
-    <t xml:space="preserve">Audience Lens Definitions  [BRAND MODULE — only if element_audience_lens = Y]</t>
+    <t xml:space="preserve">Audience Lens Definitions  [BRAND MODULE: only if element_audience_lens = Y]</t>
   </si>
   <si>
     <t xml:space="preserve">Define audience segments for side-by-side comparison across all brand metrics. AudienceID referenced by AudienceLens_Use in Brand_Config Categories sheet. Paired audiences (PairID) are shown as comparative columns. Blue rows are examples.</t>
@@ -1371,7 +1371,7 @@
     <t xml:space="preserve">[REQUIRED] Data column to test for this audience filter (e.g. BRANDPEN2_DSS, DEMO_GENDER, Focal_Category).</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] Comparison operator. Type one of: == != &gt; &lt; &gt;= &lt;= in not_in. Use 'in' / 'not_in' with comma-separated FilterValue (e.g. IPK,ROB). Note: no dropdown — &lt; and &gt; cannot be listed in Excel inline validations.</t>
+    <t xml:space="preserve">[REQUIRED] Comparison operator. Type one of: == != &gt; &lt; &gt;= &lt;= in not_in. Use 'in' / 'not_in' with comma-separated FilterValue (e.g. IPK,ROB). Note: no dropdown. &lt; and &gt; cannot be listed in Excel inline validations.</t>
   </si>
   <si>
     <t xml:space="preserve">[REQUIRED] Value(s) to compare against. For 'in' / 'not_in' operators: comma-separated list (e.g. IPK,ROB). For '==' operators: single value (e.g. IPK, 1, FEMALE).</t>
@@ -1431,7 +1431,7 @@
     <t xml:space="preserve">M</t>
   </si>
   <si>
-    <t xml:space="preserve">DBA Asset Definitions  [BRAND MODULE — only if element_dba = Y]</t>
+    <t xml:space="preserve">DBA Asset Definitions  [BRAND MODULE: only if element_dba = Y]</t>
   </si>
   <si>
     <t xml:space="preserve">Maps asset codes to their Fame and Uniqueness question codes in the data. AssetCode must match Brand_Config DBA_Assets sheet. Blue rows are examples.</t>
@@ -1524,7 +1524,7 @@
     <t xml:space="preserve">Gender, Yes/No, Preferred brand</t>
   </si>
   <si>
-    <t xml:space="preserve">Identical to Single_Mention — alternate name used in brand module</t>
+    <t xml:space="preserve">Identical to Single_Mention: alternate name used in brand module</t>
   </si>
   <si>
     <t xml:space="preserve">Same as Single_Mention</t>
@@ -1605,7 +1605,7 @@
     <t xml:space="preserve">Open_End</t>
   </si>
   <si>
-    <t xml:space="preserve">Free text — not processed in crosstabs or brand analysis</t>
+    <t xml:space="preserve">Free text: not processed in crosstabs or brand analysis</t>
   </si>
   <si>
     <t xml:space="preserve">Shown as text only; no statistical processing</t>
@@ -1617,7 +1617,7 @@
     <t xml:space="preserve">Question Code Naming Convention Guide</t>
   </si>
   <si>
-    <t xml:space="preserve">The brand module infers analytical roles from question code names automatically — no Battery or Category column needed. Follow these naming patterns exactly. This sheet is for reference only.</t>
+    <t xml:space="preserve">The brand module infers analytical roles from question code names automatically: no Battery or Category column needed. Follow these naming patterns exactly. This sheet is for reference only.</t>
   </si>
   <si>
     <t xml:space="preserve">Pattern</t>
@@ -1767,7 +1767,7 @@
     <t xml:space="preserve">CATBUY_{CAT}</t>
   </si>
   <si>
-    <t xml:space="preserve">cat_buying.frequency.{CAT}  — needs QuestionMap + OptionMap</t>
+    <t xml:space="preserve">cat_buying.frequency.{CAT}: needs QuestionMap + OptionMap</t>
   </si>
   <si>
     <t xml:space="preserve">Single_Response. Buying frequency. Add QuestionMap row + cat_buy_scale OptionMap</t>
@@ -1788,7 +1788,7 @@
     <t xml:space="preserve">CHANNEL_{CAT}</t>
   </si>
   <si>
-    <t xml:space="preserve">channel.purchase.{CAT}  — needs Channels sheet</t>
+    <t xml:space="preserve">channel.purchase.{CAT}: needs Channels sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Multi_Mention, slot-indexed. Requires Channels sheet</t>
@@ -1800,7 +1800,7 @@
     <t xml:space="preserve">PACK_DSS</t>
   </si>
   <si>
-    <t xml:space="preserve">cat_buying.packsize.{CAT}  — needs PackSizes sheet</t>
+    <t xml:space="preserve">cat_buying.packsize.{CAT}: needs PackSizes sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Multi_Mention, slot-indexed. Requires PackSizes sheet</t>
@@ -1815,7 +1815,7 @@
     <t xml:space="preserve">screener.cat_buyers_target  (slot-indexed)</t>
   </si>
   <si>
-    <t xml:space="preserve">Multi_Mention, slot-indexed. One slot per category (SQ2_1...SQ2_N — no NONE)</t>
+    <t xml:space="preserve">Multi_Mention, slot-indexed. One slot per category (SQ2_1...SQ2_N, no NONE)</t>
   </si>
   <si>
     <t xml:space="preserve">DEMO_{KEY}</t>

--- a/modules/brand/templates/Survey_Structure_Brand_Config_Template.xlsx
+++ b/modules/brand/templates/Survey_Structure_Brand_Config_Template.xlsx
@@ -207,7 +207,7 @@
     <t xml:space="preserve">Question Definitions  [SHARED: used by brand module AND tabs module]</t>
   </si>
   <si>
-    <t xml:space="preserve">One row per question. Brand module: follow the naming convention in the Question Naming Guide sheet: roles are inferred automatically from question code prefixes (BRANDAWARE_, BRANDATTR_, etc.). Tabs module: use any QuestionCode and set Variable_Type. Blue rows are examples.</t>
+    <t xml:space="preserve">One row per question. Brand module: follow the naming convention in the Question Naming Guide sheet. Roles are inferred automatically from question code prefixes (BRANDAWARE_, BRANDATTR_, etc.). Tabs module: use any QuestionCode and set Variable_Type. Blue rows are examples.</t>
   </si>
   <si>
     <t xml:space="preserve">QuestionCode</t>
@@ -255,22 +255,22 @@
     <t xml:space="preserve">[REQUIRED] Number of data columns: 1 for most types; for Multi_Mention slot-indexed questions enter the number of slots (brands + 1 for NONE). For tabs Ranking enter the number of items ranked.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] TABS: section/grouping label for output organisation (e.g. 'Demographics', 'Satisfaction'). BRAND: informational only, the brand module infers battery and category from the question code naming convention.</t>
+    <t xml:space="preserve">[Optional] TABS: section/grouping label for output organisation (e.g. 'Demographics', 'Satisfaction'). BRAND: informational only. The brand module infers battery and category from the question code naming convention.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] TABS ONLY: required for Ranking questions. 'Position' = each item column holds rank position number. 'Item' = each rank column holds item code.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] TABS ONLY, for Ranking: how many items each respondent ranks (e.g. 3 for 'rank your top 3').</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY, for Ranking: does Rank 1 mean best or worst?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY, for Numeric questions: minimum expected value (used for validation and binning).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY, for Numeric questions: maximum expected value.</t>
+    <t xml:space="preserve">[Optional] TABS ONLY: for Ranking: how many items each respondent ranks (e.g. 3 for 'rank your top 3').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY: for Ranking: does Rank 1 mean best or worst?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY: for Numeric questions: minimum expected value (used for validation and binning).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY: for Numeric questions: maximum expected value.</t>
   </si>
   <si>
     <t xml:space="preserve">[Optional] Internal notes (not shown in output).</t>
@@ -534,10 +534,10 @@
     <t xml:space="preserve">[Optional] TABS ONLY: group options into summary rows (e.g. 'Top 2 Box', 'Satisfied', 'Promoters'). Options sharing a BoxCategory label are summed.</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] TABS ONLY, for Numeric binning: minimum value of this bin (e.g. 18 for '18-24' age band).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Optional] TABS ONLY, for Numeric binning: maximum value of this bin (e.g. 24 for '18-24' age band).</t>
+    <t xml:space="preserve">[Optional] TABS ONLY: for Numeric binning: minimum value of this bin (e.g. 18 for '18-24' age band).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] TABS ONLY: for Numeric binning: maximum value of this bin (e.g. 24 for '18-24' age band).</t>
   </si>
   <si>
     <t xml:space="preserve">IPK</t>
@@ -1371,7 +1371,7 @@
     <t xml:space="preserve">[REQUIRED] Data column to test for this audience filter (e.g. BRANDPEN2_DSS, DEMO_GENDER, Focal_Category).</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] Comparison operator. Type one of: == != &gt; &lt; &gt;= &lt;= in not_in. Use 'in' / 'not_in' with comma-separated FilterValue (e.g. IPK,ROB). Note: no dropdown. &lt; and &gt; cannot be listed in Excel inline validations.</t>
+    <t xml:space="preserve">[REQUIRED] Comparison operator. Type one of: == != &gt; &lt; &gt;= &lt;= in not_in. Use 'in' / 'not_in' with comma-separated FilterValue (e.g. IPK,ROB). Note: no dropdown, because &lt; and &gt; cannot be listed in Excel inline validations.</t>
   </si>
   <si>
     <t xml:space="preserve">[REQUIRED] Value(s) to compare against. For 'in' / 'not_in' operators: comma-separated list (e.g. IPK,ROB). For '==' operators: single value (e.g. IPK, 1, FEMALE).</t>
